--- a/data/trans_dic/P33B_R4-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R4-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 27,6</t>
+          <t>19,9; 26,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,47; 38,14</t>
+          <t>32,57; 38,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 32,97</t>
+          <t>28,25; 32,27</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,63</t>
+          <t>10,67; 13,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,23</t>
+          <t>17,85; 21,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,34</t>
+          <t>14,7; 16,83</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,29</t>
+          <t>9,56; 15,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 19,7</t>
+          <t>14,8; 19,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,23</t>
+          <t>12,66; 16,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,31</t>
+          <t>12,57; 15,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 22,62</t>
+          <t>21,46; 23,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 18,2</t>
+          <t>17,43; 19,17</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>124023</t>
+          <t>133018</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264050</t>
+          <t>290761</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388072</t>
+          <t>423779</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106878; 142122</t>
+          <t>115141; 154595</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>244228; 286821</t>
+          <t>267086; 312596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363068; 417779</t>
+          <t>395069; 451354</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>245540</t>
+          <t>269252</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>373935</t>
+          <t>422228</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>619475</t>
+          <t>691480</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174371; 288896</t>
+          <t>237811; 306177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>287304; 430299</t>
+          <t>387489; 456293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505846; 694134</t>
+          <t>646906; 740581</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>84722</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113194</t>
+          <t>125816</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>186278</t>
+          <t>210538</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56773; 92246</t>
+          <t>67960; 109205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97201; 130127</t>
+          <t>108771; 146801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162811; 212027</t>
+          <t>182986; 240523</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>442647</t>
+          <t>486992</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>751179</t>
+          <t>838805</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1193825</t>
+          <t>1325797</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>349586; 493529</t>
+          <t>442132; 531673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>629153; 825783</t>
+          <t>799629; 886762</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1048625; 1292058</t>
+          <t>1262872; 1388954</t>
         </is>
       </c>
     </row>
